--- a/sutra-catalog-update.xlsx
+++ b/sutra-catalog-update.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" r:id="Ra5159cfe6b374c58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" r:id="Rbf4915b453e74247"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,18 +13,32 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="₹#,##0"/>
+  </x:numFmts>
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFAF1"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF760813"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -39,8 +53,31 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -242,348 +279,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="21.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="32.5" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13.75" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="str">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="5" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>category</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>price</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>subtitle</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>description</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>image</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>material</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>color</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>care</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="K1" s="5" t="str">
         <x:v>options</x:v>
       </x:c>
-      <x:c r="L1" t="str">
+      <x:c r="L1" s="5" t="str">
         <x:v>available</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
+    <x:row r="2" ht="78" customHeight="1">
+      <x:c r="A2" s="7" t="str">
         <x:v>cotton-saree-without-blouse</x:v>
       </x:c>
-      <x:c r="B2" t="str">
+      <x:c r="B2" s="7" t="str">
         <x:v>Cotton saree (without blouse)</x:v>
       </x:c>
-      <x:c r="C2" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D2" t="n">
+      <x:c r="C2" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D2" s="9" t="n">
         <x:v>1499</x:v>
       </x:c>
-      <x:c r="E2" t="str">
-        <x:v>Soft mulmul cotton · Without blouse</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>Lightweight, airy, and effortlessly graceful, this saree is perfect for everyday elegance, casual outings, and those who love timeless ethnic wear.
-✨ Fabric: Soft Mulmul Cotton
-🌿 Feel: Lightweight, breathable &amp; comfortable
-🤍 Style: Minimal, elegant &amp; timeless
-🌸 Perfect for: Daily wear, office wear &amp; casual occasions
-Drape yourself in comfort. Wear the elegance of simplicity.</x:v>
-      </x:c>
-      <x:c r="G2" t="str"/>
-      <x:c r="H2" t="str">
+      <x:c r="E2" s="7" t="str">
+        <x:v>Mulmul cotton · Saree only</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>Light as air and easy to wear, this mulmul cotton saree brings quiet elegance to everyday dressing. A comfortable choice for work, relaxed outings, and the simple moments in between.</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str"/>
+      <x:c r="H2" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
-      <x:c r="I2" t="str"/>
-      <x:c r="J2" t="str"/>
-      <x:c r="K2" t="str"/>
-      <x:c r="L2" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="str">
+      <x:c r="I2" s="7" t="str"/>
+      <x:c r="J2" s="7" t="str"/>
+      <x:c r="K2" s="7" t="str"/>
+      <x:c r="L2" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="78" customHeight="1">
+      <x:c r="A3" s="7" t="str">
         <x:v>mul-cotton-sarees-1499</x:v>
       </x:c>
-      <x:c r="B3" t="str">
+      <x:c r="B3" s="7" t="str">
         <x:v>Mul cotton sarees</x:v>
       </x:c>
-      <x:c r="C3" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D3" t="n">
+      <x:c r="C3" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D3" s="9" t="n">
         <x:v>1499</x:v>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E3" s="7" t="str">
         <x:v>Soft mulmul cotton</x:v>
       </x:c>
-      <x:c r="F3" t="str">
-        <x:v>Lightweight, airy, and effortlessly graceful, this saree is perfect for everyday elegance, casual outings, and those who love timeless ethnic wear.
-✨ Fabric: Soft Mulmul Cotton
-🌿 Feel: Lightweight, breathable &amp; comfortable
-🤍 Style: Minimal, elegant &amp; timeless
-🌸 Perfect for: Daily wear, office wear &amp; casual occasions
-Drape yourself in comfort. Wear the elegance of simplicity.</x:v>
-      </x:c>
-      <x:c r="G3" t="str"/>
-      <x:c r="H3" t="str">
+      <x:c r="F3" s="7" t="str">
+        <x:v>Made for long, easy days, this airy mulmul cotton saree keeps comfort at the heart of the drape. Its understated look moves naturally from office hours to casual outings.</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="str"/>
+      <x:c r="H3" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
-      <x:c r="I3" t="str"/>
-      <x:c r="J3" t="str"/>
-      <x:c r="K3" t="str"/>
-      <x:c r="L3" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="str">
+      <x:c r="I3" s="7" t="str"/>
+      <x:c r="J3" s="7" t="str"/>
+      <x:c r="K3" s="7" t="str"/>
+      <x:c r="L3" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="78" customHeight="1">
+      <x:c r="A4" s="7" t="str">
         <x:v>mulmul-cotton-lotus-embroidery-1999</x:v>
       </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="B4" s="7" t="str">
         <x:v>Mulmul cotton saree Lotus embroidery (without blouse)</x:v>
       </x:c>
-      <x:c r="C4" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D4" t="n">
+      <x:c r="C4" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D4" s="9" t="n">
         <x:v>1999</x:v>
       </x:c>
-      <x:c r="E4" t="str">
-        <x:v>Lotus embroidery · Without blouse</x:v>
-      </x:c>
-      <x:c r="F4" t="str">
-        <x:v>Lightweight, airy, and effortlessly graceful, this saree is perfect for everyday elegance, casual outings, and those who love timeless ethnic wear.
-✨ Fabric: Soft Mulmul Cotton
-🌿 Feel: Lightweight, breathable &amp; comfortable
-🤍 Style: Minimal, elegant &amp; timeless
-🌸 Perfect for: Daily wear, office wear &amp; casual occasions
-Drape yourself in comfort. Wear the elegance of simplicity.</x:v>
-      </x:c>
-      <x:c r="G4" t="str"/>
-      <x:c r="H4" t="str">
+      <x:c r="E4" s="7" t="str">
+        <x:v>Lotus embroidery · Saree only</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="str">
+        <x:v>A delicate lotus motif adds a thoughtful detail to this airy mulmul cotton saree. Lightweight and breathable, it is made for everyday wear, office days, and relaxed occasions. Saree only, blouse piece not included.</x:v>
+      </x:c>
+      <x:c r="G4" s="7" t="str"/>
+      <x:c r="H4" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
-      <x:c r="I4" t="str"/>
-      <x:c r="J4" t="str"/>
-      <x:c r="K4" t="str"/>
-      <x:c r="L4" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str">
+      <x:c r="I4" s="7" t="str"/>
+      <x:c r="J4" s="7" t="str"/>
+      <x:c r="K4" s="7" t="str"/>
+      <x:c r="L4" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="78" customHeight="1">
+      <x:c r="A5" s="7" t="str">
         <x:v>mul-cotton-sarees-1999</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B5" s="7" t="str">
         <x:v>Mul cotton sarees</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
+      <x:c r="C5" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D5" s="9" t="n">
         <x:v>1999</x:v>
       </x:c>
-      <x:c r="E5" t="str">
-        <x:v>Soft mulmul cotton</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>Lightweight, airy, and effortlessly graceful, this saree is perfect for everyday elegance, casual outings, and those who love timeless ethnic wear.
-✨ Fabric: Soft Mulmul Cotton
-🌿 Feel: Lightweight, breathable &amp; comfortable
-🤍 Style: Minimal, elegant &amp; timeless
-🌸 Perfect for: Daily wear, office wear &amp; casual occasions
-Drape yourself in comfort. Wear the elegance of simplicity</x:v>
-      </x:c>
-      <x:c r="G5" t="str"/>
-      <x:c r="H5" t="str">
+      <x:c r="E5" s="7" t="str">
+        <x:v>Lightweight mulmul cotton</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="str">
+        <x:v>An airy mulmul cotton drape with a clean, timeless feel. Soft, breathable, and easy to style, it is a comfortable companion for everyday wear and casual occasions.</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="str"/>
+      <x:c r="H5" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
-      <x:c r="I5" t="str"/>
-      <x:c r="J5" t="str"/>
-      <x:c r="K5" t="str"/>
-      <x:c r="L5" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
+      <x:c r="I5" s="7" t="str"/>
+      <x:c r="J5" s="7" t="str"/>
+      <x:c r="K5" s="7" t="str"/>
+      <x:c r="L5" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="78" customHeight="1">
+      <x:c r="A6" s="7" t="str">
         <x:v>mulmul-cotton-rose-thread-2199</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B6" s="7" t="str">
         <x:v>Mulmul cotton saree Rose thread (without blouse)</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
+      <x:c r="C6" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D6" s="9" t="n">
         <x:v>2199</x:v>
       </x:c>
-      <x:c r="E6" t="str">
-        <x:v>Rose thread embroidery · Without blouse</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
-        <x:v>Lightweight, airy, and effortlessly graceful, this saree is perfect for everyday elegance, casual outings, and those who love timeless ethnic wear.
-✨ Fabric: Soft Mulmul Cotton
-🌿 Feel: Lightweight, breathable &amp; comfortable
-🤍 Style: Minimal, elegant &amp; timeless
-🌸 Perfect for: Daily wear, office wear &amp; casual occasions
-Drape yourself in comfort. Wear the elegance of simplicity.</x:v>
-      </x:c>
-      <x:c r="G6" t="str"/>
-      <x:c r="H6" t="str">
+      <x:c r="E6" s="7" t="str">
+        <x:v>Rose threadwork · Saree only</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="str">
+        <x:v>Fine rose threadwork brings a soft accent to this lightweight mulmul cotton saree. Breathable and comfortable through the day, it suits office wear, casual outings, and everyday dressing. Saree only, blouse piece not included.</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="str"/>
+      <x:c r="H6" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
-      <x:c r="I6" t="str"/>
-      <x:c r="J6" t="str"/>
-      <x:c r="K6" t="str"/>
-      <x:c r="L6" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
+      <x:c r="I6" s="7" t="str"/>
+      <x:c r="J6" s="7" t="str"/>
+      <x:c r="K6" s="7" t="str"/>
+      <x:c r="L6" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="78" customHeight="1">
+      <x:c r="A7" s="7" t="str">
         <x:v>cotton-plain-saree</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B7" s="7" t="str">
         <x:v>Cotton plain saree</x:v>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D7" t="n">
+      <x:c r="C7" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D7" s="9" t="n">
         <x:v>799</x:v>
       </x:c>
-      <x:c r="E7" t="str">
-        <x:v>Plain cotton · Everyday comfort</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>Soft cotton, timeless charm, and elegance in every drape. 🌿✨
-A little tradition, a lot of comfort — only at Sutra.</x:v>
-      </x:c>
-      <x:c r="G7" t="str"/>
-      <x:c r="H7" t="str">
+      <x:c r="E7" s="7" t="str">
+        <x:v>Plain cotton</x:v>
+      </x:c>
+      <x:c r="F7" s="7" t="str">
+        <x:v>A simple cotton drape with a timeless feel. Soft and comfortable to wear, this plain saree brings understated elegance to everyday dressing.</x:v>
+      </x:c>
+      <x:c r="G7" s="7" t="str"/>
+      <x:c r="H7" s="7" t="str">
         <x:v>Cotton</x:v>
       </x:c>
-      <x:c r="I7" t="str"/>
-      <x:c r="J7" t="str"/>
-      <x:c r="K7" t="str"/>
-      <x:c r="L7" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
+      <x:c r="I7" s="7" t="str"/>
+      <x:c r="J7" s="7" t="str"/>
+      <x:c r="K7" s="7" t="str"/>
+      <x:c r="L7" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="78" customHeight="1">
+      <x:c r="A8" s="7" t="str">
         <x:v>cotton-leena-bhutta-saree</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B8" s="7" t="str">
         <x:v>Cotton leena bhutta saree</x:v>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D8" t="n">
+      <x:c r="C8" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D8" s="9" t="n">
         <x:v>999</x:v>
       </x:c>
-      <x:c r="E8" t="str">
-        <x:v>Cotton · Leena bhutta work</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
-        <x:v>Soft cotton, timeless charm, and elegance in every drape. 🌿✨
-A little tradition, a lot of comfort.</x:v>
-      </x:c>
-      <x:c r="G8" t="str"/>
-      <x:c r="H8" t="str">
+      <x:c r="E8" s="7" t="str">
+        <x:v>Leena bhutta · Cotton</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="str">
+        <x:v>Soft cotton meets the traditional leena bhutta motif in a saree made for comfortable everyday wear. Its subtle detailing adds a little heritage to an easy, graceful drape.</x:v>
+      </x:c>
+      <x:c r="G8" s="7" t="str"/>
+      <x:c r="H8" s="7" t="str">
         <x:v>Cotton</x:v>
       </x:c>
-      <x:c r="I8" t="str"/>
-      <x:c r="J8" t="str"/>
-      <x:c r="K8" t="str"/>
-      <x:c r="L8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
+      <x:c r="I8" s="7" t="str"/>
+      <x:c r="J8" s="7" t="str"/>
+      <x:c r="K8" s="7" t="str"/>
+      <x:c r="L8" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="78" customHeight="1">
+      <x:c r="A9" s="7" t="str">
         <x:v>mulmul-cotton-lotus-embroidery-2199</x:v>
       </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="B9" s="7" t="str">
         <x:v>Mulmul cotton saree Lotus embroidery (without blouse)</x:v>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
+      <x:c r="C9" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D9" s="9" t="n">
         <x:v>2199</x:v>
       </x:c>
-      <x:c r="E9" t="str">
-        <x:v>Lotus embroidery · Without blouse</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>Experience the timeless charm of our Mulmul Cotton Saree, crafted for those who love effortless elegance and everyday comfort.
-✨ Fabric: Soft Mulmul Cotton
-🌿 Feel: Lightweight, breathable &amp; comfortable
-🤍 Style: Minimal, elegant &amp; timeless
-🌸 Perfect for: Daily wear, office wear &amp; casual occasions♥️</x:v>
-      </x:c>
-      <x:c r="G9" t="str"/>
-      <x:c r="H9" t="str">
+      <x:c r="E9" s="7" t="str">
+        <x:v>Lotus embroidery · Saree only</x:v>
+      </x:c>
+      <x:c r="F9" s="7" t="str">
+        <x:v>Finished with lotus embroidery, this mulmul cotton saree pairs a classic detail with a light, comfortable drape. An easy choice for daily wear, office days, and casual occasions.</x:v>
+      </x:c>
+      <x:c r="G9" s="7" t="str"/>
+      <x:c r="H9" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
-      <x:c r="I9" t="str"/>
-      <x:c r="J9" t="str"/>
-      <x:c r="K9" t="str"/>
-      <x:c r="L9" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
+      <x:c r="I9" s="7" t="str"/>
+      <x:c r="J9" s="7" t="str"/>
+      <x:c r="K9" s="7" t="str"/>
+      <x:c r="L9" s="7" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="78" customHeight="1">
+      <x:c r="A10" s="7" t="str">
         <x:v>mulmul-cotton-rose-thread-2199-2</x:v>
       </x:c>
-      <x:c r="B10" t="str">
+      <x:c r="B10" s="7" t="str">
         <x:v>Mulmul cotton saree Rose thread (without blouse)</x:v>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>Timeless Sarees</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
+      <x:c r="C10" s="7" t="str">
+        <x:v>Timeless Sarees</x:v>
+      </x:c>
+      <x:c r="D10" s="9" t="n">
         <x:v>2199</x:v>
       </x:c>
-      <x:c r="E10" t="str">
-        <x:v>Rose thread embroidery · Without blouse</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>Lightweight, airy, and effortlessly graceful, this saree is perfect for everyday elegance, casual outings, and those who love timeless ethnic wear.
-✨ Fabric: Soft Mulmul Cotton
-🌿 Feel: Lightweight, breathable &amp; comfortable
-🤍 Style: Minimal, elegant &amp; timeless
-🌸 Perfect for: Daily wear, office wear &amp; casual occasions
-Drape yourself in comfort. Wear the elegance of simplicity.</x:v>
-      </x:c>
-      <x:c r="G10" t="str"/>
-      <x:c r="H10" t="str">
+      <x:c r="E10" s="7" t="str">
+        <x:v>Rose threadwork · Saree only</x:v>
+      </x:c>
+      <x:c r="F10" s="7" t="str">
+        <x:v>Delicate rose threadwork gives this breathable mulmul cotton saree a graceful finish. Light and comfortable through the day, it is an easy choice for office wear, everyday dressing, and casual outings. Saree only, blouse piece not included.</x:v>
+      </x:c>
+      <x:c r="G10" s="7" t="str"/>
+      <x:c r="H10" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
-      <x:c r="I10" t="str"/>
-      <x:c r="J10" t="str"/>
-      <x:c r="K10" t="str"/>
-      <x:c r="L10" t="str">
+      <x:c r="I10" s="7" t="str"/>
+      <x:c r="J10" s="7" t="str"/>
+      <x:c r="K10" s="7" t="str"/>
+      <x:c r="L10" s="7" t="str">
         <x:v>yes</x:v>
       </x:c>
     </x:row>

--- a/sutra-catalog-update.xlsx
+++ b/sutra-catalog-update.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" r:id="Rbf4915b453e74247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" r:id="Rcecd209f8a43456b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -286,7 +286,7 @@
     <x:col min="4" max="4" width="13.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="27.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="37.5" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18.75" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="18.75" hidden="0" customWidth="1"/>
@@ -351,7 +351,9 @@
       <x:c r="F2" s="7" t="str">
         <x:v>Light as air and easy to wear, this mulmul cotton saree brings quiet elegance to everyday dressing. A comfortable choice for work, relaxed outings, and the simple moments in between.</x:v>
       </x:c>
-      <x:c r="G2" s="7" t="str"/>
+      <x:c r="G2" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1vOXNV6BurNDLOBR3GDOxMbf2pEoQ-gWm</x:v>
+      </x:c>
       <x:c r="H2" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
@@ -381,7 +383,9 @@
       <x:c r="F3" s="7" t="str">
         <x:v>Made for long, easy days, this airy mulmul cotton saree keeps comfort at the heart of the drape. Its understated look moves naturally from office hours to casual outings.</x:v>
       </x:c>
-      <x:c r="G3" s="7" t="str"/>
+      <x:c r="G3" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1RUYGmGhsnOnMae4Jk-2c52-dg6nNIaaE</x:v>
+      </x:c>
       <x:c r="H3" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
@@ -411,7 +415,9 @@
       <x:c r="F4" s="7" t="str">
         <x:v>A delicate lotus motif adds a thoughtful detail to this airy mulmul cotton saree. Lightweight and breathable, it is made for everyday wear, office days, and relaxed occasions. Saree only, blouse piece not included.</x:v>
       </x:c>
-      <x:c r="G4" s="7" t="str"/>
+      <x:c r="G4" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1IuqVeNGpMc3oGEh8Rup9dbH6oVpQi8Tv</x:v>
+      </x:c>
       <x:c r="H4" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
@@ -441,7 +447,9 @@
       <x:c r="F5" s="7" t="str">
         <x:v>An airy mulmul cotton drape with a clean, timeless feel. Soft, breathable, and easy to style, it is a comfortable companion for everyday wear and casual occasions.</x:v>
       </x:c>
-      <x:c r="G5" s="7" t="str"/>
+      <x:c r="G5" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1rVw4WbuA21J5a104iiMJEE7hLbcSvExK</x:v>
+      </x:c>
       <x:c r="H5" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
@@ -471,7 +479,9 @@
       <x:c r="F6" s="7" t="str">
         <x:v>Fine rose threadwork brings a soft accent to this lightweight mulmul cotton saree. Breathable and comfortable through the day, it suits office wear, casual outings, and everyday dressing. Saree only, blouse piece not included.</x:v>
       </x:c>
-      <x:c r="G6" s="7" t="str"/>
+      <x:c r="G6" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=16ruUWdM7FHGKN7plfo-iq3RuBCMrJ1hi</x:v>
+      </x:c>
       <x:c r="H6" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
@@ -501,7 +511,9 @@
       <x:c r="F7" s="7" t="str">
         <x:v>A simple cotton drape with a timeless feel. Soft and comfortable to wear, this plain saree brings understated elegance to everyday dressing.</x:v>
       </x:c>
-      <x:c r="G7" s="7" t="str"/>
+      <x:c r="G7" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1vYBi1bbSzGYHAqMnsTEzOShPmd-Vas7G</x:v>
+      </x:c>
       <x:c r="H7" s="7" t="str">
         <x:v>Cotton</x:v>
       </x:c>
@@ -531,7 +543,9 @@
       <x:c r="F8" s="7" t="str">
         <x:v>Soft cotton meets the traditional leena bhutta motif in a saree made for comfortable everyday wear. Its subtle detailing adds a little heritage to an easy, graceful drape.</x:v>
       </x:c>
-      <x:c r="G8" s="7" t="str"/>
+      <x:c r="G8" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1GwjE1A3zYFL6c7W5thwZFqplNT-HMXiE</x:v>
+      </x:c>
       <x:c r="H8" s="7" t="str">
         <x:v>Cotton</x:v>
       </x:c>
@@ -561,7 +575,9 @@
       <x:c r="F9" s="7" t="str">
         <x:v>Finished with lotus embroidery, this mulmul cotton saree pairs a classic detail with a light, comfortable drape. An easy choice for daily wear, office days, and casual occasions.</x:v>
       </x:c>
-      <x:c r="G9" s="7" t="str"/>
+      <x:c r="G9" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1IuqVeNGpMc3oGEh8Rup9dbH6oVpQi8Tv</x:v>
+      </x:c>
       <x:c r="H9" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
@@ -591,7 +607,9 @@
       <x:c r="F10" s="7" t="str">
         <x:v>Delicate rose threadwork gives this breathable mulmul cotton saree a graceful finish. Light and comfortable through the day, it is an easy choice for office wear, everyday dressing, and casual outings. Saree only, blouse piece not included.</x:v>
       </x:c>
-      <x:c r="G10" s="7" t="str"/>
+      <x:c r="G10" s="7" t="str">
+        <x:v>https://drive.google.com/uc?export=view&amp;id=1gj9TFU2QgXSFd_zN37RwLhwgQFADtQak</x:v>
+      </x:c>
       <x:c r="H10" s="7" t="str">
         <x:v>Soft Mulmul Cotton</x:v>
       </x:c>
